--- a/Syllabus/EnfGeomatica/Procesamiento de imágenes y elaboración de productos cartográficos o fotogramétricos.xlsx
+++ b/Syllabus/EnfGeomatica/Procesamiento de imágenes y elaboración de productos cartográficos o fotogramétricos.xlsx
@@ -2592,25 +2592,57 @@
       <c r="J36" s="47"/>
     </row>
     <row r="37" spans="1:10" s="23" customFormat="1">
-      <c r="A37" s="64"/>
+      <c r="A37" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Comprende los fundamentos de la fotogrametría digital y de las imágenes que utiliza.</t>
+        </is>
+      </c>
       <c r="B37" s="66"/>
-      <c r="C37" s="72"/>
+      <c r="C37" s="72" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Comprender</t>
+        </is>
+      </c>
       <c r="D37" s="41"/>
       <c r="E37" s="41"/>
-      <c r="F37" s="24"/>
-      <c r="G37" s="73"/>
+      <c r="F37" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA01</t>
+        </is>
+      </c>
+      <c r="G37" s="73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Explicar los principios de la fotogrametría digital y las características y formas de adquisición de las imágenes de cámara aérea, satélite y dron.</t>
+        </is>
+      </c>
       <c r="H37" s="74"/>
       <c r="I37" s="75"/>
       <c r="J37" s="47"/>
     </row>
     <row r="38" spans="1:10" s="23" customFormat="1">
-      <c r="A38" s="64"/>
+      <c r="A38" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aplica los principios matemáticos de la fotogrametría digital.</t>
+        </is>
+      </c>
       <c r="B38" s="66"/>
-      <c r="C38" s="41"/>
+      <c r="C38" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Aplicar</t>
+        </is>
+      </c>
       <c r="D38" s="41"/>
       <c r="E38" s="41"/>
-      <c r="F38" s="24"/>
-      <c r="G38" s="73"/>
+      <c r="F38" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA02</t>
+        </is>
+      </c>
+      <c r="G38" s="73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Aplicar los modelos matemáticos de orientación y de aerotriangulación en un entorno fotogramétrico digital.</t>
+        </is>
+      </c>
       <c r="H38" s="74"/>
       <c r="I38" s="75"/>
       <c r="J38" s="47"/>
@@ -2618,23 +2650,51 @@
     <row r="39" spans="1:10" s="23" customFormat="1">
       <c r="A39" s="64"/>
       <c r="B39" s="66"/>
-      <c r="C39" s="41"/>
+      <c r="C39" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Aplicar</t>
+        </is>
+      </c>
       <c r="D39" s="41"/>
       <c r="E39" s="41"/>
-      <c r="F39" s="24"/>
-      <c r="G39" s="73"/>
+      <c r="F39" s="24" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA03</t>
+        </is>
+      </c>
+      <c r="G39" s="73" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Generar modelos digitales de terreno mediante correlación de imágenes provenientes de diferentes sensores.</t>
+        </is>
+      </c>
       <c r="H39" s="74"/>
       <c r="I39" s="75"/>
       <c r="J39" s="47"/>
     </row>
     <row r="40" spans="1:10" s="23" customFormat="1">
-      <c r="A40" s="64"/>
+      <c r="A40" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elabora productos cartográficos y fotogramétricos digitales.</t>
+        </is>
+      </c>
       <c r="B40" s="66"/>
-      <c r="C40" s="41"/>
+      <c r="C40" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Crear</t>
+        </is>
+      </c>
       <c r="D40" s="41"/>
       <c r="E40" s="41"/>
-      <c r="F40" s="16"/>
-      <c r="G40" s="64"/>
+      <c r="F40" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA04</t>
+        </is>
+      </c>
+      <c r="G40" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Elaborar productos cartográficos y fotogramétricos digitales (cartografía digital, ortofotos y ortofotomosaicos) a partir de imágenes reales procesadas en estaciones fotogramétricas.</t>
+        </is>
+      </c>
       <c r="H40" s="65"/>
       <c r="I40" s="66"/>
       <c r="J40" s="47"/>
@@ -2642,11 +2702,23 @@
     <row r="41" spans="1:10" s="23" customFormat="1">
       <c r="A41" s="64"/>
       <c r="B41" s="66"/>
-      <c r="C41" s="41"/>
+      <c r="C41" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Cognitivo - Evaluar</t>
+        </is>
+      </c>
       <c r="D41" s="41"/>
       <c r="E41" s="41"/>
-      <c r="F41" s="25"/>
-      <c r="G41" s="76"/>
+      <c r="F41" s="25" t="inlineStr">
+        <is>
+          <t xml:space="preserve">RA05</t>
+        </is>
+      </c>
+      <c r="G41" s="76" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Evaluar la calidad de los productos fotogramétricos obtenidos y seleccionar la fuente de imágenes y la solución fotogramétrica más adecuada para una aplicación.</t>
+        </is>
+      </c>
       <c r="H41" s="77"/>
       <c r="I41" s="78"/>
       <c r="J41" s="47"/>
@@ -2905,7 +2977,11 @@
       <c r="C59" s="44"/>
       <c r="D59" s="35"/>
       <c r="E59" s="35"/>
-      <c r="F59" s="35"/>
+      <c r="F59" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="G59" s="35"/>
       <c r="H59" s="35"/>
       <c r="I59" s="35"/>
@@ -2918,8 +2994,16 @@
       <c r="B60" s="44"/>
       <c r="C60" s="44"/>
       <c r="D60" s="36"/>
-      <c r="E60" s="36"/>
-      <c r="F60" s="35"/>
+      <c r="E60" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c r="F60" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="G60" s="35"/>
       <c r="H60" s="36"/>
       <c r="I60" s="35"/>
@@ -2932,9 +3016,17 @@
       <c r="B61" s="44"/>
       <c r="C61" s="44"/>
       <c r="D61" s="35"/>
-      <c r="E61" s="35"/>
+      <c r="E61" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="F61" s="35"/>
-      <c r="G61" s="35"/>
+      <c r="G61" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="H61" s="35"/>
       <c r="I61" s="36"/>
       <c r="J61" s="53"/>
@@ -2948,8 +3040,16 @@
       <c r="D62" s="35"/>
       <c r="E62" s="35"/>
       <c r="F62" s="35"/>
-      <c r="G62" s="35"/>
-      <c r="H62" s="35"/>
+      <c r="G62" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c r="H62" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="I62" s="35"/>
       <c r="J62" s="53"/>
     </row>
@@ -2963,8 +3063,16 @@
       <c r="E63" s="36"/>
       <c r="F63" s="35"/>
       <c r="G63" s="35"/>
-      <c r="H63" s="36"/>
-      <c r="I63" s="35"/>
+      <c r="H63" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
+      <c r="I63" s="35" t="inlineStr">
+        <is>
+          <t xml:space="preserve">X</t>
+        </is>
+      </c>
       <c r="J63" s="53"/>
     </row>
     <row r="64" spans="1:10">
@@ -3030,11 +3138,31 @@
       <c r="B68" s="44"/>
       <c r="C68" s="44"/>
       <c r="D68" s="36"/>
-      <c r="E68" s="36"/>
-      <c r="F68" s="36"/>
-      <c r="G68" s="36"/>
-      <c r="H68" s="36"/>
-      <c r="I68" s="36"/>
+      <c r="E68" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EHP</t>
+        </is>
+      </c>
+      <c r="F68" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EE</t>
+        </is>
+      </c>
+      <c r="G68" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EBP</t>
+        </is>
+      </c>
+      <c r="H68" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EBP</t>
+        </is>
+      </c>
+      <c r="I68" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">EOP</t>
+        </is>
+      </c>
       <c r="J68" s="53"/>
     </row>
     <row r="69" spans="1:10">
@@ -3044,11 +3172,31 @@
       <c r="B69" s="44"/>
       <c r="C69" s="44"/>
       <c r="D69" s="36"/>
-      <c r="E69" s="36"/>
-      <c r="F69" s="36"/>
-      <c r="G69" s="36"/>
-      <c r="H69" s="36"/>
-      <c r="I69" s="36"/>
+      <c r="E69" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25%</t>
+        </is>
+      </c>
+      <c r="F69" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20%</t>
+        </is>
+      </c>
+      <c r="G69" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15%</t>
+        </is>
+      </c>
+      <c r="H69" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">30%</t>
+        </is>
+      </c>
+      <c r="I69" s="36" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10%</t>
+        </is>
+      </c>
       <c r="J69" s="53"/>
     </row>
     <row r="70" spans="1:10">
@@ -3058,11 +3206,31 @@
       <c r="B70" s="44"/>
       <c r="C70" s="44"/>
       <c r="D70" s="16"/>
-      <c r="E70" s="16"/>
-      <c r="F70" s="16"/>
-      <c r="G70" s="16"/>
-      <c r="H70" s="16"/>
-      <c r="I70" s="16"/>
+      <c r="E70" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="F70" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">I</t>
+        </is>
+      </c>
+      <c r="G70" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="H70" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
+      <c r="I70" s="16" t="inlineStr">
+        <is>
+          <t xml:space="preserve">G</t>
+        </is>
+      </c>
       <c r="J70" s="53"/>
     </row>
     <row r="71" spans="1:10">
